--- a/data/trans_orig/P21-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>805792</t>
+          <t>807365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>854725</t>
+          <t>856921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>943393</t>
+          <t>937492</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1003005</t>
+          <t>1002748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1765786</t>
+          <t>1765779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1846223</t>
+          <t>1846259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32945</t>
+          <t>32609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168563</t>
+          <t>166432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217664</t>
+          <t>215038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289684</t>
+          <t>287232</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347928</t>
+          <t>352138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>470818</t>
+          <t>470746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>549698</t>
+          <t>548900</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1379581</t>
+          <t>1379637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1440872</t>
+          <t>1438743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1172945</t>
+          <t>1177650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1240819</t>
+          <t>1240794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2571556</t>
+          <t>2575008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2668113</t>
+          <t>2663856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,42 +1352,42 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>20589</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>13036</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>31358</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>20589</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>12241</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>31364</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>244519</t>
+          <t>246852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303746</t>
+          <t>303802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>333681</t>
+          <t>333373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>401818</t>
+          <t>395890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>591879</t>
+          <t>595288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>685927</t>
+          <t>683093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>452303</t>
+          <t>451784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487264</t>
+          <t>487968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>351646</t>
+          <t>351643</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>388455</t>
+          <t>388218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>813345</t>
+          <t>818223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>867257</t>
+          <t>868108</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61439</t>
+          <t>61041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96453</t>
+          <t>97326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87282</t>
+          <t>87562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124216</t>
+          <t>123916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157971</t>
+          <t>157206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209761</t>
+          <t>207270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41146</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>503666</t>
+          <t>496109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>586503</t>
+          <t>585024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>737331</t>
+          <t>742014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>835566</t>
+          <t>839809</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1262273</t>
+          <t>1265979</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1389605</t>
+          <t>1392780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>693344</t>
+          <t>695807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>748338</t>
+          <t>748271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>891840</t>
+          <t>892265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>962440</t>
+          <t>959147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1604547</t>
+          <t>1604259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1694659</t>
+          <t>1694402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56538</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43072</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>75362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>207699</t>
+          <t>206507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263876</t>
+          <t>259362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>336086</t>
+          <t>338653</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>404576</t>
+          <t>402594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>560035</t>
+          <t>559019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>646711</t>
+          <t>649188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1537051</t>
+          <t>1537034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1610666</t>
+          <t>1613917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1267653</t>
+          <t>1264724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1339984</t>
+          <t>1342154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2823019</t>
+          <t>2828257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2929926</t>
+          <t>2931829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>38911</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>330862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>404653</t>
+          <t>406796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>405028</t>
+          <t>402892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>475067</t>
+          <t>480728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>760120</t>
+          <t>759124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>864645</t>
+          <t>862863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>394731</t>
+          <t>395012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>426344</t>
+          <t>426152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>323846</t>
+          <t>322759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>361414</t>
+          <t>361255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>728201</t>
+          <t>729420</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>781983</t>
+          <t>780546</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>956</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4755</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5255</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86450</t>
+          <t>86169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96151</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133813</t>
+          <t>134196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157276</t>
+          <t>158794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210538</t>
+          <t>210307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2658728</t>
+          <t>2664679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2759071</t>
+          <t>2762845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2518518</t>
+          <t>2513225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2626073</t>
+          <t>2623799</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5204331</t>
+          <t>5203905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5346405</t>
+          <t>5356024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>48027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39975</t>
+          <t>38848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69684</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69296</t>
+          <t>69902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106498</t>
+          <t>105554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>624833</t>
+          <t>623338</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>722556</t>
+          <t>719219</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>871548</t>
+          <t>873916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>978261</t>
+          <t>983405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1538584</t>
+          <t>1524193</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1677697</t>
+          <t>1675845</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>592249</t>
+          <t>591991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>633413</t>
+          <t>631891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>734711</t>
+          <t>737153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>788342</t>
+          <t>790950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1345608</t>
+          <t>1342985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1412412</t>
+          <t>1409532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26651</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38570</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>29741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57481</t>
+          <t>56737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102449</t>
+          <t>103649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143168</t>
+          <t>141921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>177938</t>
+          <t>176803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231079</t>
+          <t>227870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>289407</t>
+          <t>294371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>355786</t>
+          <t>358406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1687813</t>
+          <t>1684282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1758904</t>
+          <t>1754588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1557392</t>
+          <t>1558080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1627045</t>
+          <t>1626199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3263008</t>
+          <t>3268395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3366288</t>
+          <t>3362338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40266</t>
+          <t>40899</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35714</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38329</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69198</t>
+          <t>70191</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283323</t>
+          <t>288046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>352769</t>
+          <t>359510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>336522</t>
+          <t>336024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>404887</t>
+          <t>402794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>640060</t>
+          <t>642055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>736888</t>
+          <t>733808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>451250</t>
+          <t>451494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486276</t>
+          <t>485654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>389109</t>
+          <t>390305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>429642</t>
+          <t>431796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>853896</t>
+          <t>854437</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>906882</t>
+          <t>908763</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57595</t>
+          <t>58428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92254</t>
+          <t>92415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107097</t>
+          <t>106760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148277</t>
+          <t>146072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171990</t>
+          <t>172140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223559</t>
+          <t>222764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2762085</t>
+          <t>2755999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2851142</t>
+          <t>2849727</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2716613</t>
+          <t>2717185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2810674</t>
+          <t>2815743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5512107</t>
+          <t>5508957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5648328</t>
+          <t>5644505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45060</t>
+          <t>46143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77574</t>
+          <t>78088</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87009</t>
+          <t>88586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129989</t>
+          <t>131693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>471481</t>
+          <t>476137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558943</t>
+          <t>562671</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>655064</t>
+          <t>649467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744840</t>
+          <t>746983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1142705</t>
+          <t>1142591</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1275894</t>
+          <t>1273567</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>363295</t>
+          <t>360405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>400401</t>
+          <t>399338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>513460</t>
+          <t>513188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>551650</t>
+          <t>550786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>887238</t>
+          <t>887766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>940847</t>
+          <t>939585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106453</t>
+          <t>108607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143269</t>
+          <t>146603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>181162</t>
+          <t>181608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>215994</t>
+          <t>218046</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>299750</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>351082</t>
+          <t>353020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1821263</t>
+          <t>1819344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2000192</t>
+          <t>2012147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1141952</t>
+          <t>1192551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1756671</t>
+          <t>1753252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2867504</t>
+          <t>2963042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3668799</t>
+          <t>3684800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20532</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286516</t>
+          <t>272236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>460930</t>
+          <t>463260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>472495</t>
+          <t>474325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1086433</t>
+          <t>1038995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>842534</t>
+          <t>828737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1645419</t>
+          <t>1553087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>481158</t>
+          <t>478272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>528563</t>
+          <t>526373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>465805</t>
+          <t>465625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>507463</t>
+          <t>508398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>963651</t>
+          <t>962669</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1023879</t>
+          <t>1024411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112026</t>
+          <t>114384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160193</t>
+          <t>161863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148982</t>
+          <t>148164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>191272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273954</t>
+          <t>274134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334065</t>
+          <t>334465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2702215</t>
+          <t>2698474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2925142</t>
+          <t>2906645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2114165</t>
+          <t>2120130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2768339</t>
+          <t>2777056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4840389</t>
+          <t>4816337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5584635</t>
+          <t>5585617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>28796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38667</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35241</t>
+          <t>36488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60098</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>506993</t>
+          <t>526845</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>730802</t>
+          <t>731310</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>848684</t>
+          <t>838722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1508011</t>
+          <t>1500751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1462292</t>
+          <t>1463565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2208522</t>
+          <t>2241049</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>807365</t>
+          <t>806840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>856921</t>
+          <t>857643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>937492</t>
+          <t>938598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1002748</t>
+          <t>1005557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1765779</t>
+          <t>1763837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1846259</t>
+          <t>1849226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32609</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>43204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>166432</t>
+          <t>165259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>215038</t>
+          <t>215601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287232</t>
+          <t>287101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>352138</t>
+          <t>351008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>470746</t>
+          <t>466958</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>548900</t>
+          <t>550306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1379637</t>
+          <t>1372549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1438743</t>
+          <t>1436595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1177650</t>
+          <t>1178663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1240794</t>
+          <t>1243956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2575008</t>
+          <t>2570812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2663856</t>
+          <t>2668591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20708</t>
+          <t>21087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>246852</t>
+          <t>247102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303802</t>
+          <t>309433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>333373</t>
+          <t>330012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>395890</t>
+          <t>394900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>595288</t>
+          <t>590169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>683093</t>
+          <t>685203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>451784</t>
+          <t>452663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487968</t>
+          <t>487876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,82 +1660,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>82,09%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>370317</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>350707</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>387166</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>77,73%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>73,61%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>842117</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>814069</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>866104</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>81,93%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>370317</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>351643</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>388218</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>77,73%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>73,81%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>81,49%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>842117</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>818223</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>868108</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>81,93%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61041</t>
+          <t>61872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97326</t>
+          <t>95835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87562</t>
+          <t>88343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123916</t>
+          <t>124839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157206</t>
+          <t>158681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207270</t>
+          <t>210499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50323</t>
+          <t>49881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41643</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71984</t>
+          <t>71617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>496109</t>
+          <t>500866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>585024</t>
+          <t>584583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>742014</t>
+          <t>735146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839809</t>
+          <t>833843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1265979</t>
+          <t>1262898</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1392780</t>
+          <t>1398898</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>695807</t>
+          <t>693609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>748271</t>
+          <t>748362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>892265</t>
+          <t>891591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>959147</t>
+          <t>960576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1604259</t>
+          <t>1604954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1694402</t>
+          <t>1690754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>55011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75362</t>
+          <t>76961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206507</t>
+          <t>208798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>259362</t>
+          <t>261950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>338653</t>
+          <t>336234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>402594</t>
+          <t>403928</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>559019</t>
+          <t>561294</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>649188</t>
+          <t>648422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1537034</t>
+          <t>1538945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1613917</t>
+          <t>1611354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1264724</t>
+          <t>1261643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1342154</t>
+          <t>1339247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2828257</t>
+          <t>2829896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2931829</t>
+          <t>2929282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,82 +3372,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>18919</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>27431</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>18862</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>39297</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>10579</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>5253</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>18872</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>27431</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>18525</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>38911</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>330862</t>
+          <t>334435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>406796</t>
+          <t>405990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>402892</t>
+          <t>406377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>480728</t>
+          <t>481754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>759124</t>
+          <t>760732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>862863</t>
+          <t>859730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395012</t>
+          <t>394263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>426152</t>
+          <t>427065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>322759</t>
+          <t>323810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>361255</t>
+          <t>363834</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>729420</t>
+          <t>730899</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>780546</t>
+          <t>781414</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>54116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86169</t>
+          <t>86918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96403</t>
+          <t>94039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134196</t>
+          <t>134146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158794</t>
+          <t>157638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210307</t>
+          <t>208043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2664679</t>
+          <t>2659869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2762845</t>
+          <t>2761779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2513225</t>
+          <t>2518736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2623799</t>
+          <t>2626730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5203905</t>
+          <t>5208790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5356024</t>
+          <t>5358328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38848</t>
+          <t>38631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69902</t>
+          <t>68549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>107091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>623338</t>
+          <t>621996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>719219</t>
+          <t>721338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>873916</t>
+          <t>872587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>983405</t>
+          <t>978646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1524193</t>
+          <t>1522457</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1675845</t>
+          <t>1672834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>591991</t>
+          <t>592683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>631891</t>
+          <t>632815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>737153</t>
+          <t>738821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>790950</t>
+          <t>791139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1342985</t>
+          <t>1340901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1409532</t>
+          <t>1413277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>57145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103649</t>
+          <t>103173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141921</t>
+          <t>142101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>176803</t>
+          <t>176349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>227870</t>
+          <t>225954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>294371</t>
+          <t>291484</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>358406</t>
+          <t>359153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1684282</t>
+          <t>1691272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1754588</t>
+          <t>1760268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1558080</t>
+          <t>1555751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1626199</t>
+          <t>1628932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3268395</t>
+          <t>3267187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3362338</t>
+          <t>3367120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39884</t>
+          <t>39463</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70191</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>288046</t>
+          <t>281320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359510</t>
+          <t>351270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>336024</t>
+          <t>335014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>402794</t>
+          <t>407717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>642055</t>
+          <t>638051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>733808</t>
+          <t>735438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>451494</t>
+          <t>451677</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>485654</t>
+          <t>485625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>390305</t>
+          <t>390207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>431796</t>
+          <t>430660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>854437</t>
+          <t>853082</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>908763</t>
+          <t>906737</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58428</t>
+          <t>58301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92415</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>105628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146072</t>
+          <t>144370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172140</t>
+          <t>173338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222764</t>
+          <t>226564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2755999</t>
+          <t>2759589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2849727</t>
+          <t>2848605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,82 +6226,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>81,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2768524</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2721187</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2812630</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>78,53%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>77,18%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5574654</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>5506219</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5641598</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>79,89%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>81,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2768524</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2717185</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2815743</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>78,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>77,07%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5296</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5574654</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>5508957</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5644505</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>62814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46143</t>
+          <t>46278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78088</t>
+          <t>78126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88586</t>
+          <t>88097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131693</t>
+          <t>129154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>476137</t>
+          <t>470450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>562671</t>
+          <t>555852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>649467</t>
+          <t>650257</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>746983</t>
+          <t>740578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1142591</t>
+          <t>1144082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1273567</t>
+          <t>1274523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>381993</t>
+          <t>437013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>360405</t>
+          <t>414350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>399338</t>
+          <t>456170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>532545</t>
+          <t>579821</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>513188</t>
+          <t>560626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>550786</t>
+          <t>599649</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>914538</t>
+          <t>1016835</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>887766</t>
+          <t>989690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>939585</t>
+          <t>1044153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,27 +7041,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28180</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>125349</t>
+          <t>133650</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108607</t>
+          <t>115876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146603</t>
+          <t>155048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>199399</t>
+          <t>218108</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>181608</t>
+          <t>199602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218046</t>
+          <t>236694</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>324747</t>
+          <t>351758</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>325273</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>353020</t>
+          <t>379404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>751513</t>
+          <t>819490</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>751513</t>
+          <t>819490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>751513</t>
+          <t>819490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1266451</t>
+          <t>1398020</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1266451</t>
+          <t>1398020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1266451</t>
+          <t>1398020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1886470</t>
+          <t>1799083</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1819344</t>
+          <t>1757737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2012147</t>
+          <t>1842235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1579278</t>
+          <t>1664710</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1192551</t>
+          <t>1625688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1753252</t>
+          <t>1697840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3465748</t>
+          <t>3463793</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2963042</t>
+          <t>3408251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3684800</t>
+          <t>3521749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>396466</t>
+          <t>423281</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>272236</t>
+          <t>381338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>463260</t>
+          <t>466216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>649417</t>
+          <t>495752</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>474325</t>
+          <t>462183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1038995</t>
+          <t>534410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1045883</t>
+          <t>919032</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>828737</t>
+          <t>863704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1553087</t>
+          <t>975420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2234228</t>
+          <t>2167728</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2234228</t>
+          <t>2167728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2234228</t>
+          <t>2167728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4524555</t>
+          <t>4398294</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4524555</t>
+          <t>4398294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4524555</t>
+          <t>4398294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>505451</t>
+          <t>550302</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>478272</t>
+          <t>523585</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>526373</t>
+          <t>574217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>488411</t>
+          <t>543909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>465625</t>
+          <t>520566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>508398</t>
+          <t>565367</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>993862</t>
+          <t>1094210</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>962669</t>
+          <t>1056941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1024411</t>
+          <t>1125262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>134940</t>
+          <t>154654</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114384</t>
+          <t>130518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161863</t>
+          <t>180492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>168409</t>
+          <t>186729</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148164</t>
+          <t>164798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191272</t>
+          <t>210074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>303349</t>
+          <t>341383</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274134</t>
+          <t>310366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334465</t>
+          <t>378153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>709617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>709617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>709617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1304458</t>
+          <t>1443621</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1304458</t>
+          <t>1443621</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1304458</t>
+          <t>1443621</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2773914</t>
+          <t>2786398</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2698474</t>
+          <t>2730973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2906645</t>
+          <t>2835436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2600234</t>
+          <t>2788439</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2120130</t>
+          <t>2740015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2777056</t>
+          <t>2836316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5374148</t>
+          <t>5574837</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4816337</t>
+          <t>5504588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5585617</t>
+          <t>5643698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>30763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47337</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>67416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>656755</t>
+          <t>711584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>526845</t>
+          <t>662588</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>731310</t>
+          <t>766948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1017224</t>
+          <t>900589</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838722</t>
+          <t>852614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1500751</t>
+          <t>947327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1673979</t>
+          <t>1612173</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1463565</t>
+          <t>1541508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2241049</t>
+          <t>1682253</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3450136</t>
+          <t>3518712</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3450136</t>
+          <t>3518712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450136</t>
+          <t>3518712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3645328</t>
+          <t>3721222</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3645328</t>
+          <t>3721222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3645328</t>
+          <t>3721222</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7095464</t>
+          <t>7239935</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7095464</t>
+          <t>7239935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7095464</t>
+          <t>7239935</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
